--- a/media/system/system_test_case.xlsx
+++ b/media/system/system_test_case.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="236">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t xml:space="preserve">is_file_required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
   </si>
   <si>
     <t xml:space="preserve">4G WAN Interface</t>
@@ -62,6 +65,9 @@
   </si>
   <si>
     <t xml:space="preserve">{"cellular_interface": "wwan1", "remote_ping_ip": "8.8.8.8", "test_duration" : "60", "error_threshold_percent":"10"}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puspendra</t>
   </si>
   <si>
     <t xml:space="preserve">4G PCI/Cell Lock</t>
@@ -151,8 +157,7 @@
 7. Verify that the DUT attached to the specified cell.</t>
   </si>
   <si>
-    <t xml:space="preserve">{"cellular_interface": "wwan1", "remote_ping_ip": "8.8.8.8"}
-</t>
+    <t xml:space="preserve">{"cellular_interface": "wwan1", "error_threshold_percent":"10"}</t>
   </si>
   <si>
     <t xml:space="preserve">5G PCI/Cell Unlock</t>
@@ -169,9 +174,6 @@
 6. Verify that the DUT PCI Lock is Disable.</t>
   </si>
   <si>
-    <t xml:space="preserve">{"cellular_interface": "wwan1", "error_threshold_percent":"10"}</t>
-  </si>
-  <si>
     <t xml:space="preserve">5G Band Lock</t>
   </si>
   <si>
@@ -190,7 +192,7 @@
     <t xml:space="preserve">Dual 4G/5G WAN</t>
   </si>
   <si>
-    <t xml:space="preserve">BB-TRF-4G5G-004</t>
+    <t xml:space="preserve">BB- TRF-4G5G-004</t>
   </si>
   <si>
     <t xml:space="preserve">4G/5G Cellular WAN</t>
@@ -206,13 +208,13 @@
     <t xml:space="preserve">{"wan4g_interface":"wwan0","wan5g_interface":"wwan1","remote_ping_ip":"8.8.8.8","test_duration":"60","error_threshold_percent":"10"}</t>
   </si>
   <si>
-    <t xml:space="preserve">WAN BONDING 4G/5G</t>
+    <t xml:space="preserve">Multi-WAN (Cellular &amp; Ethernet)</t>
   </si>
   <si>
     <t xml:space="preserve">BB-TRF-BND-001</t>
   </si>
   <si>
-    <t xml:space="preserve">WAN BONDING RESILIENCY</t>
+    <t xml:space="preserve">MultiWAN</t>
   </si>
   <si>
     <t xml:space="preserve">1. Setup MWAN3 bonding policy for primary and backup WAN interfaces.
@@ -224,7 +226,7 @@
     <t xml:space="preserve">{"primary_iface": "wan", "backup_iface":"wan1", "primary_weight":"1", "backup_weight":"1", "mode":"bonding"}</t>
   </si>
   <si>
-    <t xml:space="preserve">WAN Bonding 4G/5G and WWAN</t>
+    <t xml:space="preserve">Multi-WAN (Cellular &amp; Ethernet &amp; WWAN)</t>
   </si>
   <si>
     <t xml:space="preserve">BB-TRF-BND-002</t>
@@ -239,7 +241,7 @@
     <t xml:space="preserve">{"primary_iface":"wan","backup_iface":"wan2","tertiary_iface":"wan3","primary_weight":"1","backup_weight":"1","tertiary_weight":"1", "mode":"bonding"}</t>
   </si>
   <si>
-    <t xml:space="preserve">WAN Bonding Resiliency</t>
+    <t xml:space="preserve">Multi-WAN Resiliency</t>
   </si>
   <si>
     <t xml:space="preserve">BB-TRF-BND-003</t>
@@ -421,7 +423,7 @@
     <t xml:space="preserve">{"PC":{"name":"Data Center","ip":"192.168.100.10","user":"osboxes","password":"osboxes.org","device_id":"GZafjCj0g0h0POHlSM7IlHzJ2jFFT4oj","execution_id":"1","connection_protocol":"SSH"},"L2TP_DUT":[{"underlay_iface":"eth1","local_ip":"10.1.1.15","remote_ip":"10.10.10.10","tunnel_id":"1","session_id":"1000","peer_tunnel_id":"1","peer_session_id":"1000","overlay_ip":"192.168.201.9","udp_sport":"6000","udp_dport":"5000"},{"underlay_iface":"eth2","local_ip":"10.2.2.15","remote_ip":"10.20.20.10","tunnel_id":"2","session_id":"2000","peer_tunnel_id":"2","peer_session_id":"2000","overlay_ip":"192.168.202.9","udp_sport":"6001","udp_dport":"5001"}],"L2TP_PC":[{"underlay_iface":"ens3","local_ip":"10.10.10.10","remote_ip":"10.1.1.15","tunnel_id":"1","session_id":"1000","peer_tunnel_id":"1","peer_session_id":"1000","overlay_ip":"192.168.201.10","udp_sport":"5000","udp_dport":"6000"},{"underlay_iface":"ens4","local_ip":"10.20.20.10","remote_ip":"10.2.2.15","tunnel_id":"2","session_id":"2000","peer_tunnel_id":"2","peer_session_id":"2000","overlay_ip":"192.168.202.10","udp_sport":"5001","udp_dport":"6001"}],"dut_lo_ip":"192.168.250.15","pc_lo_ip":"192.168.250.10"}</t>
   </si>
   <si>
-    <t xml:space="preserve">eth-static</t>
+    <t xml:space="preserve">Ethernet (LAN) Interface  – Static</t>
   </si>
   <si>
     <t xml:space="preserve">BB-INT-ETH-001</t>
@@ -449,7 +451,7 @@
       "ip": "100.91.48.105",
       "user": "rbp5user",
       "password": "rbp5!@#",
-      "eth0_ip":"192.168.1.100/24",
+      "eth0_ip":"192.168.0.100/24",
       "gateway":"192.168.104.1",
       "device_id": "WhWtsQF0vWRZzFOby0rHDU1QanU5HPKh",
       "execution_id": "2",
@@ -459,7 +461,7 @@
       "name": "RPI2",
       "ip": "100.72.200.49",
       "user": "rbp5user",
-      "eth0_ip":"192.168.1.120/24",
+      "eth0_ip":"192.168.0.120/24",
       "gateway":"192.168.104.1",
       "password": "rbp5!@#",
       "device_id": "IUjU4TdS9eSZpXAl8yWboW4aAUVBpAaF",
@@ -475,7 +477,10 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">eth-dynamic</t>
+    <t xml:space="preserve">Kalyani</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethernet (LAN) Interface  – Dynamic</t>
   </si>
   <si>
     <t xml:space="preserve">BB-INT-ETH-002</t>
@@ -521,7 +526,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wifi-static</t>
+    <t xml:space="preserve">WLAN Interface – Static</t>
   </si>
   <si>
     <t xml:space="preserve">BB-INT-WLAN-001</t>
@@ -574,7 +579,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wifi-dynamic</t>
+    <t xml:space="preserve">WLAN Interface – Dynamic</t>
   </si>
   <si>
     <t xml:space="preserve">BB-INT-WLAN-002</t>
@@ -620,7 +625,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wifi -traffic2</t>
+    <t xml:space="preserve">Wi-Fi (LAN) ↔ Wi-Fi (WAN)</t>
   </si>
   <si>
     <t xml:space="preserve">BB-TRF-WWAN-002</t>
@@ -681,7 +686,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wifi interface</t>
+    <t xml:space="preserve">Wi-Fi WAN Interface</t>
   </si>
   <si>
     <t xml:space="preserve">BB-INT-WWAN-001</t>
@@ -729,7 +734,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wif-throughput</t>
+    <t xml:space="preserve">WLAN Interface L2 Throughput</t>
   </si>
   <si>
     <t xml:space="preserve">BB-INT-WLAN-003</t>
@@ -751,7 +756,7 @@
 8.ping checks among all devices to verify connectivity.</t>
   </si>
   <si>
-    <t xml:space="preserve">wifi-wan</t>
+    <t xml:space="preserve">Ethernet (LAN) ↔ Wi-Fi (WAN)</t>
   </si>
   <si>
     <t xml:space="preserve">BB-TRF-WWAN-001</t>
@@ -766,7 +771,7 @@
 7. Collect post-test DUT stats, consolidate logs (pings, iperf, monitoring, tcpdump), and close all connections.</t>
   </si>
   <si>
-    <t xml:space="preserve">ethernet-bridging</t>
+    <t xml:space="preserve">	Ethernet (LAN) bridging</t>
   </si>
   <si>
     <t xml:space="preserve">BB-TRF-BRG-001</t>
@@ -814,7 +819,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">wifi tarffic</t>
+    <t xml:space="preserve">Ethernet (LAN) ↔ Wi-Fi (LAN) bridging</t>
   </si>
   <si>
     <t xml:space="preserve">BB-TRF-BRG-002</t>
@@ -897,8 +902,8 @@
 4.Check that the VRF is successfully created on DUT.
 5.Check that the VRF is successfully created on PE2.
 6.Ping from CE1 to CE2 to verify connectivity.
-7.Ping from CE2 to CE1 to verify reverse connectivity.
-8.Pass the test if VRF creation and both ping tests are successful.</t>
+7.Ping from CE2 to CE1 to verify to check  connectivity.
+</t>
   </si>
   <si>
     <t xml:space="preserve">{
@@ -978,7 +983,7 @@
   }</t>
   </si>
   <si>
-    <t xml:space="preserve">Access_Control</t>
+    <t xml:space="preserve">Access_Control_via_SSH</t>
   </si>
   <si>
     <t xml:space="preserve">BB-SEC-ACC-001</t>
@@ -1194,7 +1199,7 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">CDM-BB Inventory check</t>
+    <t xml:space="preserve">Inventory check</t>
   </si>
   <si>
     <t xml:space="preserve">BB-SU-006</t>
@@ -1266,7 +1271,7 @@
 5. If reset behavior is correct, mark test as PASSED.</t>
   </si>
   <si>
-    <t xml:space="preserve">SD Card slot</t>
+    <t xml:space="preserve">SD Card Test</t>
   </si>
   <si>
     <t xml:space="preserve">BB-SU-008</t>
@@ -1416,7 +1421,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1442,6 +1447,14 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="0"/>
       <charset val="1"/>
@@ -1517,12 +1530,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1546,11 +1563,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1558,7 +1575,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1639,7 +1656,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="14.45" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.71"/>
@@ -1649,9 +1666,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="35.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="23.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.28"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1673,885 +1691,996 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" s="2" customFormat="true" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" s="3" customFormat="true" ht="218.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" s="4" customFormat="true" ht="100.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="G2" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5" t="s">
+    </row>
+    <row r="3" s="5" customFormat="true" ht="100.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="5" t="s">
+      <c r="B3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" s="4" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="E3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="G3" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="5" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" s="4" customFormat="true" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="5" customFormat="true" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="5" t="s">
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" s="4" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
+      <c r="C5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="G5" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" s="5" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="5" customFormat="true" ht="72" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="E6" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" s="6" customFormat="true" ht="76.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="C7" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="5" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="F7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" s="6" customFormat="true" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="5" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="E8" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="G8" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" s="6" customFormat="true" ht="91.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" s="4" customFormat="true" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="C9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="E9" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" s="5" customFormat="true" ht="57.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" s="4" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="C10" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="G10" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" s="5" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="true" ht="144" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" s="5" customFormat="true" ht="144" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="5" t="s">
+      <c r="D12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" s="4" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
+      <c r="E12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="G12" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" s="5" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="true" ht="86.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="G13" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="true" ht="76.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="5" t="s">
+      <c r="B14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="C14" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="4" customFormat="true" ht="129.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="E14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="G14" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" s="5" customFormat="true" ht="129.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="5" t="s">
+      <c r="B15" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="5" t="s">
+      <c r="C15" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="4" customFormat="true" ht="213" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="G15" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" s="5" customFormat="true" ht="213" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="5" t="s">
+      <c r="B16" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="C16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="E16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="4" customFormat="true" ht="244.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="F16" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="G16" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" s="5" customFormat="true" ht="244.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="B17" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E17" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F17" s="5" t="s">
+      <c r="C17" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="4" customFormat="true" ht="290.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="s">
+      <c r="E17" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="G17" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" s="5" customFormat="true" ht="290.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" s="5" t="s">
+      <c r="B18" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F18" s="5" t="s">
+      <c r="C18" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="true" ht="201.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="E18" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="G18" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" s="5" customFormat="true" ht="201.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="4" customFormat="true" ht="316.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+      <c r="E19" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="G19" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" s="5" customFormat="true" ht="316.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="B20" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="E20" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F20" s="5" t="s">
+      <c r="C20" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="4" customFormat="true" ht="244.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
+      <c r="E20" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="G20" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" s="5" customFormat="true" ht="244.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="5" t="s">
+      <c r="D21" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" s="4" customFormat="true" ht="302.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+      <c r="E21" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="G21" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" s="5" customFormat="true" ht="302.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="B22" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="5" t="s">
+      <c r="C22" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="4" customFormat="true" ht="273.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="E22" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="G22" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" s="5" customFormat="true" ht="273.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="E23" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F23" s="5" t="s">
+      <c r="D23" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" s="4" customFormat="true" ht="409.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="E23" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="G23" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" s="5" customFormat="true" ht="409.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="B24" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E24" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="5" t="s">
+      <c r="C24" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
+      <c r="E24" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="9" t="s">
         <v>105</v>
       </c>
+      <c r="D25" s="10" t="s">
+        <v>106</v>
+      </c>
       <c r="E25" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>106</v>
+        <v>66</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>107</v>
       </c>
       <c r="G25" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="H25" s="0" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>107</v>
+      <c r="A26" s="10" t="s">
+        <v>109</v>
       </c>
       <c r="B26" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="0" t="s">
         <v>108</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="G26" s="0" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="0" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>116</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>115</v>
+        <v>66</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H27" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="0" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>119</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>120</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>119</v>
+        <v>66</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>121</v>
       </c>
       <c r="G28" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H28" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="0" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>122</v>
+        <v>115</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>124</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>123</v>
+        <v>66</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="G29" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H29" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>126</v>
+        <v>115</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>128</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>127</v>
+        <v>66</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="G30" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="0" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B31" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C31" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>127</v>
-      </c>
       <c r="G31" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="0" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>133</v>
+        <v>115</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>135</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>127</v>
+        <v>66</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>129</v>
       </c>
       <c r="G32" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>139</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>138</v>
+        <v>66</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>140</v>
       </c>
       <c r="G33" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
+      <c r="H33" s="0" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>139</v>
+      <c r="A34" s="10" t="s">
+        <v>141</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>113</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>141</v>
+        <v>115</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>143</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F34" s="9" t="s">
-        <v>142</v>
+        <v>66</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>144</v>
       </c>
       <c r="G34" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H34" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="0" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C35" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>145</v>
+        <v>138</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>147</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>110</v>
+        <v>66</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>112</v>
       </c>
       <c r="G35" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H35" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="409.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="0" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="D36" s="9" t="s">
         <v>148</v>
       </c>
+      <c r="D36" s="10" t="s">
+        <v>150</v>
+      </c>
       <c r="E36" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F36" s="9" t="s">
-        <v>149</v>
+        <v>66</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>151</v>
       </c>
       <c r="G36" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H36" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="275.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C37" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>154</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>153</v>
+        <v>66</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>155</v>
       </c>
       <c r="G37" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
+      </c>
+      <c r="H37" s="0" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="198" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>159</v>
       </c>
       <c r="E38" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>158</v>
+        <v>66</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>160</v>
       </c>
       <c r="G38" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2560,22 +2689,22 @@
     </row>
     <row r="39" customFormat="false" ht="213" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="D39" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>162</v>
+        <v>66</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>164</v>
       </c>
       <c r="G39" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2584,22 +2713,22 @@
     </row>
     <row r="40" customFormat="false" ht="259.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>163</v>
-      </c>
-      <c r="D40" s="9" t="s">
         <v>165</v>
       </c>
+      <c r="D40" s="10" t="s">
+        <v>167</v>
+      </c>
       <c r="E40" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F40" s="9" t="s">
-        <v>166</v>
+        <v>66</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>168</v>
       </c>
       <c r="G40" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2608,46 +2737,46 @@
     </row>
     <row r="41" customFormat="false" ht="198" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>169</v>
+        <v>158</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>171</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F41" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="G41" s="0" t="n">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="229.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="C42" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="G41" s="0" t="n">
-        <f aca="false">FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="229.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="B42" s="0" t="s">
-        <v>171</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>172</v>
+      <c r="D42" s="10" t="s">
+        <v>174</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>173</v>
+        <v>66</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>175</v>
       </c>
       <c r="G42" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2656,19 +2785,19 @@
     </row>
     <row r="43" customFormat="false" ht="198" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C43" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D43" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>11</v>
+        <v>178</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="G43" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2677,21 +2806,21 @@
     </row>
     <row r="44" customFormat="false" ht="91.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="0" t="s">
+        <v>180</v>
+      </c>
+      <c r="B44" s="0" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B44" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D44" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F44" s="9"/>
+      <c r="D44" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="10"/>
       <c r="G44" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
@@ -2699,22 +2828,22 @@
     </row>
     <row r="45" customFormat="false" ht="91.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C45" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>184</v>
+        <v>178</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>186</v>
       </c>
       <c r="G45" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2723,22 +2852,22 @@
     </row>
     <row r="46" customFormat="false" ht="91.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D46" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F46" s="9" t="s">
-        <v>188</v>
+        <v>178</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>190</v>
       </c>
       <c r="G46" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2747,22 +2876,22 @@
     </row>
     <row r="47" customFormat="false" ht="121.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F47" s="9" t="s">
-        <v>192</v>
+        <v>178</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>194</v>
       </c>
       <c r="G47" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2771,22 +2900,22 @@
     </row>
     <row r="48" customFormat="false" ht="106.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D48" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>196</v>
+        <v>178</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>198</v>
       </c>
       <c r="G48" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2795,22 +2924,22 @@
     </row>
     <row r="49" customFormat="false" ht="91.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="D49" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F49" s="9" t="s">
         <v>201</v>
+      </c>
+      <c r="D49" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>203</v>
       </c>
       <c r="G49" s="0" t="n">
         <f aca="false">TRUE()</f>
@@ -2819,21 +2948,21 @@
     </row>
     <row r="50" customFormat="false" ht="76.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D50" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F50" s="9"/>
+        <v>178</v>
+      </c>
+      <c r="D50" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="10"/>
       <c r="G50" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
@@ -2841,21 +2970,21 @@
     </row>
     <row r="51" customFormat="false" ht="137.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>176</v>
-      </c>
-      <c r="D51" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F51" s="9"/>
+        <v>178</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="10"/>
       <c r="G51" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
@@ -2863,22 +2992,22 @@
     </row>
     <row r="52" customFormat="false" ht="121.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>199</v>
-      </c>
-      <c r="D52" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>211</v>
+        <v>201</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>213</v>
       </c>
       <c r="G52" s="0" t="n">
         <f aca="false">TRUE()</f>
@@ -2887,21 +3016,21 @@
     </row>
     <row r="53" customFormat="false" ht="106.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="D53" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F53" s="9"/>
+        <v>216</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="10"/>
       <c r="G53" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
@@ -2909,21 +3038,21 @@
     </row>
     <row r="54" customFormat="false" ht="106.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="0" t="s">
+        <v>218</v>
+      </c>
+      <c r="B54" s="0" t="s">
+        <v>219</v>
+      </c>
+      <c r="C54" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="B54" s="0" t="s">
-        <v>217</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F54" s="9"/>
+      <c r="D54" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="10"/>
       <c r="G54" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
@@ -2931,21 +3060,21 @@
     </row>
     <row r="55" customFormat="false" ht="259.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>219</v>
-      </c>
-      <c r="D55" s="9" t="s">
         <v>221</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F55" s="9"/>
+      <c r="D55" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="10"/>
       <c r="G55" s="0" t="n">
         <f aca="false">FALSE()</f>
         <v>0</v>
@@ -2953,19 +3082,19 @@
     </row>
     <row r="56" customFormat="false" ht="183" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="0" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="D56" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E56" s="4" t="s">
-        <v>11</v>
+        <v>216</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="G56" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2974,19 +3103,19 @@
     </row>
     <row r="57" customFormat="false" ht="91.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="0" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="D57" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>11</v>
+        <v>216</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="G57" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -2995,19 +3124,19 @@
     </row>
     <row r="58" customFormat="false" ht="106.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="0" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="D58" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>11</v>
+        <v>216</v>
+      </c>
+      <c r="D58" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="G58" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -3016,19 +3145,19 @@
     </row>
     <row r="59" customFormat="false" ht="183" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="0" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>214</v>
-      </c>
-      <c r="D59" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>11</v>
+        <v>216</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="G59" s="0" t="n">
         <f aca="false">FALSE()</f>
@@ -3037,10 +3166,10 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
